--- a/partner_results/chebi/ClassMissingGermanDefinition_chebi.xlsx
+++ b/partner_results/chebi/ClassMissingGermanDefinition_chebi.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rubber particle [chebi]</t>
+          <t>hydrocarbylene group [chebi]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>polymer [chebi]</t>
+          <t>organodiyl group [chebi]</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A polymer consisting of cis-linked prenyl units.</t>
+          <t>A bivalent group formed by removing two hydrogen atoms from a hydrocarbon, the free valencies of which are not engaged in a double bond.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hydrocarbylene group [chebi]</t>
+          <t>polymer [chebi]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>organodiyl group [chebi]</t>
+          <t>mixture [chebi]</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A bivalent group formed by removing two hydrogen atoms from a hydrocarbon, the free valencies of which are not engaged in a double bond.</t>
+          <t>A polymer is a mixture, which is composed of macromolecules of different kinds and which may be differentiated by composition, length, degree of branching etc..</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -484,18 +484,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>thiazoles [chebi]</t>
+          <t>mixture [chebi]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>organosulfur heterocyclic compound</t>
+          <t>chemical substance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>An azole in which the five-membered heterocyclic aromatic skeleton contains a N atom and one S atom.</t>
+          <t>A mixture is a chemical substance composed of multiple molecules, at least two of which are of a different kind.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -503,37 +503,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>organic divalent group [chebi]</t>
+          <t>dithiocarbamate [chebi]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>organic group [chebi]</t>
+          <t>dithiocarbamate anions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lars Vogt</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Luis Ramos</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A member of the class of dithiocarbamate anions resulting from the deprotonation of both of the dithiocarbamic acid moieties of ethylenebis(dithiocarbamic acid). The major species at pH 7.3.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mixture [chebi]</t>
+          <t>plasticizer [chebi]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>role</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A mixture is a chemical substance composed of multiple molecules, at least two of which are of a different kind.</t>
+          <t>Any compound that is used as an additive to increase the plasticity or fluidity of a substance, particularly but not exclusively to synthetic polymers.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -541,18 +545,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>polymer [chebi]</t>
+          <t>organic divalent group [chebi]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>mixture [chebi]</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>organic group [chebi]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lars Vogt</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A polymer is a mixture, which is composed of macromolecules of different kinds and which may be differentiated by composition, length, degree of branching etc..</t>
+          <t>Definition not available</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -560,18 +568,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>plasticizer [chebi]</t>
+          <t>organic group [chebi]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>group [chebi]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Any compound that is used as an additive to increase the plasticity or fluidity of a substance, particularly but not exclusively to synthetic polymers.</t>
+          <t>Any substituent group or skeleton containing carbon.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -579,18 +587,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>carbon black [chebi]</t>
+          <t>di(benzothiazol-2-yl)disulfide [chebi]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>elemental carbon</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>organic disulfide</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Luis Ramos</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>An elemental carbon in the form of virtually pure colloidal particles that are produced by incomplete combustion or thermal decomposition of gaseous or liquid hydrocarbons under controlled conditions. A black, finely divided pellet or powder, its properties of specific surface area, particle size and structure, conductivity and colour can be varied by varying the exact conditions for its production. It is used in tyres, rubber and plastic products, printing inks and coatings.</t>
+          <t>An organic disulfide resulting from the formal oxidative coupling of the thiol groups of two molecules of 1,3-benzothiazole-2-thiol. It is used as an accelerator in the rubber industry.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -598,22 +610,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>di(benzothiazol-2-yl)disulfide [chebi]</t>
+          <t>thiazoles [chebi]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>organic disulfide</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Luis Ramos</t>
-        </is>
-      </c>
+          <t>azole</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>An organic disulfide resulting from the formal oxidative coupling of the thiol groups of two molecules of 1,3-benzothiazole-2-thiol. It is used as an accelerator in the rubber industry.</t>
+          <t>An azole in which the five-membered heterocyclic aromatic skeleton contains a N atom and one S atom.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -621,22 +629,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dithiocarbamate [chebi]</t>
+          <t>organodiyl group [chebi]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dithiocarbamate anions</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Luis Ramos</t>
-        </is>
-      </c>
+          <t>organic divalent group [chebi]</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A member of the class of dithiocarbamate anions resulting from the deprotonation of both of the dithiocarbamic acid moieties of ethylenebis(dithiocarbamic acid). The major species at pH 7.3.</t>
+          <t>Any organic substituent group, regardless of functional type, having two free valences at carbon atom(s).</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -644,18 +648,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>organodiyl group [chebi]</t>
+          <t>group [chebi]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>organic divalent group [chebi]</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>chemical entity</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Luis Ramos</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Any organic substituent group, regardless of functional type, having two free valences at carbon atom(s).</t>
+          <t>A defined linked collection of atoms or a single atom within a molecular entity.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -663,18 +671,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>organic group [chebi]</t>
+          <t>rubber particle [chebi]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>group [chebi]</t>
+          <t>polymer [chebi]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Any substituent group or skeleton containing carbon.</t>
+          <t>A polymer consisting of cis-linked prenyl units.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -682,22 +690,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>group [chebi]</t>
+          <t>carbon black [chebi]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>chemical entity</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Luis Ramos</t>
-        </is>
-      </c>
+          <t>elemental carbon</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>A defined linked collection of atoms or a single atom within a molecular entity.</t>
+          <t>An elemental carbon in the form of virtually pure colloidal particles that are produced by incomplete combustion or thermal decomposition of gaseous or liquid hydrocarbons under controlled conditions. A black, finely divided pellet or powder, its properties of specific surface area, particle size and structure, conductivity and colour can be varied by varying the exact conditions for its production. It is used in tyres, rubber and plastic products, printing inks and coatings.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
